--- a/server/data/imports/uber/uber.xlsx
+++ b/server/data/imports/uber/uber.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V32\server\data\imports\uber\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V39\server\data\imports\uber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAF0678-6331-4989-A874-D10702E23485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F2F561-D59B-4CCC-AE12-BFDCCB98E083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A100726-893B-4AF6-887A-6E8D99DEE1FA}"/>
   </bookViews>
@@ -468,7 +468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0258365A-ED26-4117-A724-7F37F5D696E5}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:N158"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -2690,6 +2690,34 @@
         <v>969</v>
       </c>
     </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="2">
+        <v>46205</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <v>214</v>
+      </c>
+      <c r="D159">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B160">
+        <v>56</v>
+      </c>
+      <c r="C160">
+        <v>492</v>
+      </c>
+      <c r="D160">
+        <v>1712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/server/data/imports/uber/uber.xlsx
+++ b/server/data/imports/uber/uber.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V39\server\data\imports\uber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F2F561-D59B-4CCC-AE12-BFDCCB98E083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79E9386D-5A0F-41E4-AAE8-808CD49D0B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A100726-893B-4AF6-887A-6E8D99DEE1FA}"/>
   </bookViews>
@@ -468,7 +468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0258365A-ED26-4117-A724-7F37F5D696E5}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N162"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -2715,7 +2715,35 @@
         <v>492</v>
       </c>
       <c r="D160">
-        <v>1712</v>
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="2">
+        <v>46207</v>
+      </c>
+      <c r="B161">
+        <v>41</v>
+      </c>
+      <c r="C161">
+        <v>760</v>
+      </c>
+      <c r="D161">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="2">
+        <v>46208</v>
+      </c>
+      <c r="B162">
+        <v>49</v>
+      </c>
+      <c r="C162">
+        <v>640</v>
+      </c>
+      <c r="D162">
+        <v>705</v>
       </c>
     </row>
   </sheetData>
